--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -776,9 +776,9 @@
           <t>Story drafted from code/docs</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Partially tested - pass</t>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Tested - pass</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Login page visible with email/password/sign-in controls. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.</t>
+          <t>Authenticated disposable manager reached dashboard and user menu. Evidence: RUN-003 e2e/authenticated-flow.spec.ts.</t>
         </is>
       </c>
     </row>
@@ -849,14 +849,14 @@
           <t>Story drafted from code/docs</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Not tested in story loop</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Tested - pass</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Signout cleared browser flow back to login. Evidence: RUN-003 e2e/authenticated-flow.spec.ts.</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13873,6 +13873,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RUN-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Credentialed login and logout</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/authenticated-flow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with disposable Supabase manager user</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TW-002 pass, TW-003 pass</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Terminal output; disposable auth user deleted by test cleanup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No defects recorded for this run</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -13887,7 +13934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13996,6 +14043,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Last testing progress</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RUN-003 authenticated login/logout passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -1289,23 +1289,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Pass after fix (RUN-006)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Browser e2e passed after DEF-001 fix</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; ManagerTriageDashboard unit; role-journeys manager dashboard/admin e2e</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>DEF-001</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; RUN-004 exposed contradictory lead-gap safety copy; fixed and retested in RUN-005/RUN-006</t>
         </is>
       </c>
     </row>
@@ -1435,23 +1439,23 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Pass (RUN-006)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Browser e2e passed for manager navigation/admin surfaces</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; role-journeys manager planning/admin surfaces e2e</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; RUN-006 covered dashboard, availability manager, team, requests, user-access approval, settings, audit log, work patterns, and directory navigation</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13708,6 +13712,68 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DEF-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TW-009</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fixed and retested</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>/dashboard/manager</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Manager dashboard could show '1 shift missing a lead today' while the checklist said 'Covered today' / no coverage safety issue; the e2e assertion still expected old coverage-copy text.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>The Make today safe checklist should include missing-lead risk and direct managers to assign visible leads before routine planning.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Run role-journeys manager planning/admin surfaces before the fix, or load manager dashboard with today staffed but one visible lead missing.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>RUN-004 failed 12/13 role journeys at manager dashboard copy; RUN-005 focused retest passed; RUN-006 full role-journeys retest passed.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Fixed by aligning checklist safety state with missing-lead attention state and updating stale e2e expectation.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Pending commit in current working tree</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Pass: ManagerTriageDashboard unit 14/14; focused manager planning/admin e2e 1/1; full role-journeys e2e 13/13.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -13722,7 +13788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13917,6 +13983,147 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>No defects recorded for this run</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RUN-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-22 pre-fix</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full role journeys before dashboard safety-copy fix</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase service-backed role journey setup</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fail: 12/13 passed; manager planning/admin surfaces failed on stale dashboard safety-copy assertion</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TW-009 failed, TW-011 blocked by dashboard assertion; other passed role journeys require story-by-story tracker mapping</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>test-results/role-journeys-role-journey-0d241-planning-and-admin-surfaces-chromium/error-context.md; trace.zip (not retained after cleanup)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Failure revealed real UX contradiction: missing-lead priority card while checklist claimed the day was covered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RUN-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:58</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Focused manager dashboard safety-copy regression and manager planning/admin retest</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run src/components/manager/ManagerTriageDashboard.test.ts; npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1 --grep "manager can reach the planning and admin surfaces"</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Local Vitest and Playwright chromium with Supabase role journey setup</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass: unit 14/14; focused e2e 1/1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TW-009 pass after fix; TW-011 focused pass</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Terminal output; Playwright artifacts not retained after cleanup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DEF-001 retested against the exact failed manager journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RUN-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-22 22:11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full role journeys after dashboard safety-copy fix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase service-backed role journey setup</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass: 13/13 tests</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TW-009 pass, TW-011 pass; additional role journeys pending story-by-story tracker mapping</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Terminal output; Playwright artifacts not retained after cleanup</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Confirmed the repaired manager dashboard/admin path did not regress the broader role journey suite.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -705,23 +705,23 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-009)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/public-pages.spec.ts landing page CTA click coverage</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Root / landing page heading rendered; main-content Sign in CTA navigated to /login; main-content Request access CTA navigated to /signup. Evidence: RUN-009.</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Partially tested - pass</t>
+          <t>Tested - pass (RUN-009)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Signup page visible with Request access heading and Submit request control. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.</t>
+          <t>Signup page visible with Request access heading and Submit request control. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Signup page still renders Request access heading and Submit request control in RUN-009.</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Partially tested - pass</t>
+          <t>Partially tested - pass (RUN-009)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser responsive public auth test passed; broader responsive matrix pending</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.</t>
+          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Public login/signup mobile controls remained touch-safe and overflow-free in RUN-009.</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14124,6 +14124,147 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>Confirmed the repaired manager dashboard/admin path did not regress the broader role journey suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RUN-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-23 10:44</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Public landing navigation exploratory e2e after adding root CTA test</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fail: new landing test strict-mode locator matched both header and hero Sign in links; existing login/signup/mobile tests passed</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TW-001 test harness failure; TW-004 pass; TW-060 pass</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>test-results/public-pages-landing-page-exposes-public-navigation-chromium/error-context.md before cleanup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No product defect recorded; locator needed to scope the story to main-content CTA rather than public header navigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RUN-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-23 10:51</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Focused public landing navigation after main-content locator fix</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1 --grep "landing page exposes public navigation"</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass: focused landing CTA click test 1/1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TW-001 pass</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Terminal output; Playwright artifacts not retained after cleanup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Validated root heading plus Sign in and Request access CTA clicks from main content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RUN-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-23 10:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Public landing/login/signup browser suite</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass: 4/4 tests</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TW-001 pass; TW-004 pass; TW-060 partial pass</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Terminal output; Playwright artifacts not retained after cleanup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Final public-pages suite includes root landing CTA clicks, login render, signup render, and mobile touch-safe auth controls.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -87,6 +87,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -997,23 +1000,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-044)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/public-pages.spec.ts password reset submit-flow coverage</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>DEF-003</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Password reset tested from login link through hydrated recover POST mock, generic success copy, and Back to sign in. Evidence: RUN-043/RUN-044; DEF-003 fixed.</t>
         </is>
       </c>
     </row>
@@ -1070,23 +1077,23 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-011)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/staff-onboarding.spec.ts</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pending/setup gate covered by staff onboarding e2e. Evidence: RUN-011.</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1223,23 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-011)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/staff-onboarding.spec.ts</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Staff onboarding checklist/setup flows covered. Evidence: RUN-011.</t>
         </is>
       </c>
     </row>
@@ -1366,23 +1373,23 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-029)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/staff-dashboard-smoke.spec.ts</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Staff dashboard next-step messaging and due state covered. Evidence: RUN-029.</t>
         </is>
       </c>
     </row>
@@ -1512,23 +1519,23 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-027)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/therapist-schedule-trust-smoke.spec.ts</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Staff schedule navigation and schedule trust flows covered. Evidence: RUN-027.</t>
         </is>
       </c>
     </row>
@@ -1585,23 +1592,23 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-019)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/schedule-block-planning.spec.ts</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Future block planning covered. Evidence: RUN-019.</t>
         </is>
       </c>
     </row>
@@ -1658,23 +1665,23 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-019)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/schedule-block-planning.spec.ts; e2e/manager-availability-planner.spec.ts</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Availability due date visibility and locked availability behavior covered. Evidence: RUN-019/RUN-012.</t>
         </is>
       </c>
     </row>
@@ -1731,23 +1738,23 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-016)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-controls.spec.ts</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager draft cycle opening covered from unified Schedule grid. Evidence: RUN-016.</t>
         </is>
       </c>
     </row>
@@ -1804,23 +1811,23 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-018)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts; e2e/coverage-display.spec.ts</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Role-specific schedule grid controls covered for manager, lead, and therapist. Evidence: RUN-017/RUN-018.</t>
         </is>
       </c>
     </row>
@@ -1877,23 +1884,23 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-027)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts; e2e/therapist-schedule-trust-smoke.spec.ts</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Day/night tab and query override coverage recorded. Evidence: RUN-018/RUN-027.</t>
         </is>
       </c>
     </row>
@@ -1950,23 +1957,23 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-018)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts; e2e/post-final-grid-edits.spec.ts</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manual assignment and final schedule add-staff paths covered. Evidence: RUN-018/RUN-035.</t>
         </is>
       </c>
     </row>
@@ -2023,23 +2030,23 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-018)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Unassign path covered. Evidence: RUN-018.</t>
         </is>
       </c>
     </row>
@@ -2096,23 +2103,23 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-018)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Inline designated lead path covered. Evidence: RUN-018.</t>
         </is>
       </c>
     </row>
@@ -2169,23 +2176,23 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-017)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-display.spec.ts</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Schedule status/display states covered across staff/lead/manager views. Evidence: RUN-017.</t>
         </is>
       </c>
     </row>
@@ -2242,23 +2249,23 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-018)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-schedule-roster.spec.ts</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Published assignment status updates and staffing totals covered. Evidence: RUN-018.</t>
         </is>
       </c>
     </row>
@@ -2388,23 +2395,23 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-021)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-proactive-risk.spec.ts</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pre-flight auto-draft risk prompt covered. Evidence: RUN-021.</t>
         </is>
       </c>
     </row>
@@ -2461,23 +2468,23 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-016)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-controls.spec.ts; e2e/coverage-proactive-risk.spec.ts</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Auto-draft from unified Schedule grid and risk prompt covered. Evidence: RUN-016/RUN-021.</t>
         </is>
       </c>
     </row>
@@ -2534,23 +2541,23 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-016)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-controls.spec.ts</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Draft cycle delete/restart path covered. Evidence: RUN-016.</t>
         </is>
       </c>
     </row>
@@ -2607,23 +2614,23 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Skipped - legacy coverage only (RUN-020)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Skipped; no current behavior pass evidence</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-templates.spec.ts skipped</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Legacy cycle-template controls are no longer exposed on unified Schedule grid; story needs current product decision or new coverage. Evidence: RUN-020.</t>
         </is>
       </c>
     </row>
@@ -2680,23 +2687,23 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-023)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-history-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Republish/offline lifecycle coverage includes publishing an offline cycle. Evidence: RUN-023.</t>
         </is>
       </c>
     </row>
@@ -2753,23 +2760,23 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-023)</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-history-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Publish history details and deletion covered. Evidence: RUN-023.</t>
         </is>
       </c>
     </row>
@@ -2826,23 +2833,23 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-023)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-history-lifecycle.spec.ts; e2e/manager-specialized-controls.spec.ts</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Live/offline and archive lifecycle covered. Evidence: RUN-023/RUN-033.</t>
         </is>
       </c>
     </row>
@@ -2899,23 +2906,23 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-026)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/therapist-recurring-pattern-flow.spec.ts</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Therapist recurring pattern save paths covered. Evidence: RUN-026.</t>
         </is>
       </c>
     </row>
@@ -2972,23 +2979,23 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-027)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/therapist-recurring-pattern-flow.spec.ts; e2e/therapist-schedule-trust-smoke.spec.ts</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Availability draft generation and Need Off note persistence covered. Evidence: RUN-026/RUN-027.</t>
         </is>
       </c>
     </row>
@@ -3045,23 +3052,23 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-027)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/therapist-schedule-trust-smoke.spec.ts; e2e/need-off-markers.spec.ts</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Submitted availability detail and Need Off markers covered. Evidence: RUN-027/RUN-028.</t>
         </is>
       </c>
     </row>
@@ -3118,23 +3125,23 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Partially tested - pass (RUN-014)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser partial pass; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/availability-override.spec.ts</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Assignment validation rejects unavailable/PRN-not-offered cases; direct therapist conflict-warning UI still needs a story-specific assertion. Evidence: RUN-014.</t>
         </is>
       </c>
     </row>
@@ -3191,23 +3198,23 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-012)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts; e2e/need-off-markers.spec.ts</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager availability planner, hard-date saving, and submitted marker visibility covered. Evidence: RUN-012/RUN-028.</t>
         </is>
       </c>
     </row>
@@ -3264,23 +3271,23 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Partially tested - pass (RUN-012)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser partial pass; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Missing-responder focus/cycle switch covered; reminder delivery/send path not yet directly asserted. Evidence: RUN-012.</t>
         </is>
       </c>
     </row>
@@ -3556,23 +3563,23 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-034)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/team-quick-edit.spec.ts</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Team roster quick edit, archive/deactivate, role checklist, FMLA return clearing covered. Evidence: RUN-034.</t>
         </is>
       </c>
     </row>
@@ -3921,23 +3928,27 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass after fix (RUN-045)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/requests-workflow.spec.ts</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>DEF-002</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pickup request creation from My Requests now follows current board-review copy and passed full workflow retest. Evidence: RUN-013 failure, RUN-045 pass.</t>
         </is>
       </c>
     </row>
@@ -3994,23 +4005,23 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-045)</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/requests-workflow.spec.ts; e2e/pickup-interest-concurrency.spec.ts</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Team-visible pickup/swap request paths and claimant queue behavior covered. Evidence: RUN-031/RUN-045.</t>
         </is>
       </c>
     </row>
@@ -4067,23 +4078,23 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-045)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/requests-workflow.spec.ts; e2e/pickup-interest-concurrency.spec.ts</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.</t>
         </is>
       </c>
     </row>
@@ -4140,23 +4151,23 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-045)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/requests-workflow.spec.ts; e2e/pickup-interest-concurrency.spec.ts</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.</t>
         </is>
       </c>
     </row>
@@ -4213,23 +4224,23 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-032)</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/staff-personal-pages.spec.ts</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Therapist History page renders seeded live data. Evidence: RUN-032.</t>
         </is>
       </c>
     </row>
@@ -4286,23 +4297,23 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-038)</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/lottery-workflow.spec.ts; e2e/lottery-operational-flow.spec.ts; e2e/lottery-workflow-surface.spec.ts</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Lottery navigation, request, fix-list, preview/apply, audit, and history paths covered. Evidence: RUN-024/RUN-025/RUN-038.</t>
         </is>
       </c>
     </row>
@@ -4359,23 +4370,23 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Partially tested - pass (RUN-035)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser partial pass; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Therapist notification creation after final grid edit covered; feed read/mark-read behavior still needs direct assertions. Evidence: RUN-035.</t>
         </is>
       </c>
     </row>
@@ -4505,23 +4516,23 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Partially tested - pass (RUN-035)</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser partial pass; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts; e2e/lottery-operational-flow.spec.ts</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Operational audit entries observed through schedule/lottery flows; dedicated audit-log page still needs direct route coverage. Evidence: RUN-025/RUN-035.</t>
         </is>
       </c>
     </row>
@@ -4724,23 +4735,23 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-039)</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/directory-redirect.spec.ts; e2e/coverage-cycle-controls.spec.ts; e2e/manager-schedule-roster.spec.ts</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Legacy/compatibility redirects covered including /directory and old coverage/schedule routes. Evidence: RUN-016/RUN-018/RUN-039.</t>
         </is>
       </c>
     </row>
@@ -4870,23 +4881,23 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-036)</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated browser test passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-process-api.spec.ts</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Publish process API auth and idempotency covered. Evidence: RUN-036.</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4954,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Tested - pass</t>
+          <t>Tested - pass (RUN-039)</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4953,13 +4964,13 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/auth-redirect.spec.ts; e2e/proxy-routing.spec.ts; e2e/directory-redirect.spec.ts</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Protected routes /dashboard, /dashboard/manager, /dashboard/staff, /availability, /schedule, /shift-board, /profile redirect to /login. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.</t>
+          <t>Protected routes /dashboard, /dashboard/manager, /dashboard/staff, /availability, /schedule, /shift-board, /profile redirect to /login. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Protected-route, proxy, and directory redirect guards covered. Evidence: RUN-002/RUN-037/RUN-039.</t>
         </is>
       </c>
     </row>
@@ -5016,23 +5027,23 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-009)</t>
+          <t>Partially tested - pass (RUN-044)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Automated browser responsive public auth test passed; broader responsive matrix pending</t>
+          <t>Automated browser partial pass; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/public-pages.spec.ts; e2e/coverage-display.spec.ts</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Public login/signup mobile controls remained touch-safe and overflow-free in RUN-009.</t>
+          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Public login/signup mobile controls remained touch-safe and overflow-free in RUN-009.; Public auth mobile/touch safety and selected schedule display coverage recorded. Evidence: RUN-017/RUN-044.</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7524,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-014</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7542,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-010</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7560,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-016</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7578,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: skipped legacy surface RUN-020</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7596,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-017</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7614,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: skipped legacy surface RUN-040</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7632,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-021</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7654,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: skipped legacy surface RUN-015</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7676,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: skipped allowlisted demo seed RUN-041</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7698,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-039</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7720,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-025</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7742,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-038</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7764,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-024</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7786,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-022</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7808,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-012</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7830,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-018</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7852,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-033</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7870,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-028</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7888,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-031</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7906,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-035</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7924,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-030</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7942,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-037</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7964,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed and expanded in testing loop: RUN-042/RUN-044</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7986,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-023</t>
         </is>
       </c>
     </row>
@@ -7997,7 +8008,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-036</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8030,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed and fixed in testing loop: RUN-013/RUN-045</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8070,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-019</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8092,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-029</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8114,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-011</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8136,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-032</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8158,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-034</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8180,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-026</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8202,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed in testing loop: RUN-027</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13765,12 +13776,136 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Pending commit in current working tree</t>
+          <t>52284839 Keep manager safety triage consistent</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Pass: ManagerTriageDashboard unit 14/14; focused manager planning/admin e2e 1/1; full role-journeys e2e 13/13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>DEF-002</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>TW-045</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Fixed and retested</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>/requests/new, /shift-board</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Requests workflow e2e timed out waiting for old "Post to the board" copy after the app had already advanced to the current Review board request step.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>The test should follow the current board-request CTA and verify the pickup request lifecycle through creation.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Run e2e/requests-workflow.spec.ts before the fix; requester pickup path fails around the board-review step.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>RUN-013 failed on stale test copy; RUN-045 passed the full requests workflow after the copy fix.</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Logistical test error; product flow exposed the current Review board request step.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Current tracker/test progress change set</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Pass: full requests-workflow e2e 6/7 with 1 intentional seeded fixture skip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>DEF-003</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>TW-005</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Fixed and retested</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>/reset-password</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Initial reset-password e2e clicked the form before client hydration and used an ambiguous Back to sign in locator shared by header and form footer.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>The test should exercise the hydrated client reset flow, capture exactly one recover POST, assert generic success copy, and scope navigation back to login.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Run the first public-pages reset test attempt before hardening.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>RUN-042 failed; RUN-043 focused reset retest passed; RUN-044 full public suite passed.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Logistical browser-test error while adding missing story coverage; not a product defect.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Current tracker/test progress change set</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Pass: focused reset e2e 1/1 and full public-pages e2e 5/5.</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13893,378 +14028,2070 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>RUN-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>2026-06-22 21:08</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Public auth rendering, mobile auth controls, unauthenticated protected-route redirects</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts e2e/auth-redirect.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium via repo webServer</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Pass: 10/10 tests</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>TW-002 partial, TW-004 partial, TW-059 pass, TW-060 partial</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Terminal output; no screenshot artifact retained</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>No defects recorded for this run</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>RUN-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>2026-06-22 21:26</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Credentialed login and logout</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/authenticated-flow.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium with disposable Supabase manager user</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Pass: 1/1 test</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>TW-002 pass, TW-003 pass</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Terminal output; disposable auth user deleted by test cleanup</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>No defects recorded for this run</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>RUN-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>2026-06-22 pre-fix</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Full role journeys before dashboard safety-copy fix</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium with Supabase service-backed role journey setup</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Fail: 12/13 passed; manager planning/admin surfaces failed on stale dashboard safety-copy assertion</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>TW-009 failed, TW-011 blocked by dashboard assertion; other passed role journeys require story-by-story tracker mapping</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>test-results/role-journeys-role-journey-0d241-planning-and-admin-surfaces-chromium/error-context.md; trace.zip (not retained after cleanup)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Failure revealed real UX contradiction: missing-lead priority card while checklist claimed the day was covered.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RUN-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>2026-06-22 21:58</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Focused manager dashboard safety-copy regression and manager planning/admin retest</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>npx.cmd vitest run src/components/manager/ManagerTriageDashboard.test.ts; npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1 --grep "manager can reach the planning and admin surfaces"</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Local Vitest and Playwright chromium with Supabase role journey setup</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Pass: unit 14/14; focused e2e 1/1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>TW-009 pass after fix; TW-011 focused pass</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Terminal output; Playwright artifacts not retained after cleanup</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>DEF-001 retested against the exact failed manager journey.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>RUN-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>2026-06-22 22:11</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Full role journeys after dashboard safety-copy fix</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/role-journeys.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium with Supabase service-backed role journey setup</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Pass: 13/13 tests</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>TW-009 pass, TW-011 pass; additional role journeys pending story-by-story tracker mapping</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Terminal output; Playwright artifacts not retained after cleanup</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Confirmed the repaired manager dashboard/admin path did not regress the broader role journey suite.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>RUN-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>2026-06-23 10:44</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Public landing navigation exploratory e2e after adding root CTA test</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium via repo webServer</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Fail: new landing test strict-mode locator matched both header and hero Sign in links; existing login/signup/mobile tests passed</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>TW-001 test harness failure; TW-004 pass; TW-060 pass</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>test-results/public-pages-landing-page-exposes-public-navigation-chromium/error-context.md before cleanup</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>No product defect recorded; locator needed to scope the story to main-content CTA rather than public header navigation.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>RUN-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>2026-06-23 10:51</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Focused public landing navigation after main-content locator fix</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1 --grep "landing page exposes public navigation"</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium via repo webServer</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pass: focused landing CTA click test 1/1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>TW-001 pass</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Terminal output; Playwright artifacts not retained after cleanup</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Validated root heading plus Sign in and Request access CTA clicks from main content.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>RUN-009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>2026-06-23 10:55</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Public landing/login/signup browser suite</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Local Playwright chromium via repo webServer</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Pass: 4/4 tests</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>TW-001 pass; TW-004 pass; TW-060 partial pass</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Terminal output; Playwright artifacts not retained after cleanup</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Final public-pages suite includes root landing CTA clicks, login render, signup render, and mobile touch-safe auth controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>RUN-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Button/navigation audit including reset route reachability</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/button-navigation-audit.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>TW-005 route reached; route-only evidence</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>RUN-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Staff onboarding gate and setup flows</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/staff-onboarding.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 4/4 tests</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>TW-006 pass; TW-008 pass</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>RUN-012</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Manager availability planner</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/manager-availability-planner.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 3/3 tests</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>TW-035 pass; TW-036 partial; TW-014 partial; TW-026 partial</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>RUN-013</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Requests workflow before stale copy fix</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/requests-workflow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Fail: requester pickup request path timed out on old button copy</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>TW-045 failed by stale test harness</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>The app was already on Review board request; test still waited for old Post to the board button. See DEF-002.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RUN-014</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Availability override assignment validation</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/availability-override.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 tests</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>TW-018 partial; TW-034 partial</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>RUN-015</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Legacy coverage publish flow</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-publish-flow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Skipped: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>No story pass evidence</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>RUN-016</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Coverage cycle controls</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-cycle-controls.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 3/3 tests</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>TW-015 pass; TW-025 pass; TW-026 pass; TW-056 pass</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>RUN-017</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Coverage display and role-specific schedule grid controls</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-display.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 4/5 tests; 1 skipped legacy badge check</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>TW-016 pass; TW-017 pass; TW-021 pass; TW-060 partial</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>RUN-018</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Manager schedule roster operations</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/manager-schedule-roster.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 6/6 tests</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>TW-016 pass; TW-017 pass; TW-018 pass; TW-019 pass; TW-020 pass; TW-022 pass; TW-056 pass</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>RUN-019</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Schedule block planning and visibility</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/schedule-block-planning.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>TW-013 pass; TW-014 pass</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>RUN-020</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Legacy coverage cycle templates</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-cycle-templates.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Skipped: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>TW-027 no current pass evidence</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>RUN-021</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Coverage proactive auto-draft risk prompt</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-proactive-risk.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>TW-024 pass; TW-025 partial</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RUN-022</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Manager assignment picker eligibility</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/manager-assignment-picker-eligibility.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>TW-018 partial</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>RUN-023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Publish history lifecycle</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/publish-history-lifecycle.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 4/4 tests</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>TW-028 pass; TW-029 pass; TW-030 pass</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>RUN-024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Lottery workflow</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/lottery-workflow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>TW-050 pass</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>RUN-025</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Lottery operational flow</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/lottery-operational-flow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>TW-050 pass; TW-053 partial</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>RUN-026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Therapist recurring patterns</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/therapist-recurring-pattern-flow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 tests</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>TW-031 pass; TW-032 partial</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>RUN-027</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Therapist schedule trust smoke</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/therapist-schedule-trust-smoke.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 8/8 tests</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>TW-012 pass; TW-017 pass; TW-032 pass; TW-033 pass; TW-049 partial</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>RUN-028</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Need Off markers</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/need-off-markers.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>TW-033 partial; TW-035 partial</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>RUN-029</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Staff dashboard smoke</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/staff-dashboard-smoke.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>TW-010 pass</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>RUN-030</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Preliminary pencil marks</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/preliminary-pencil-marks.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>TW-047 partial; TW-048 partial</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>RUN-031</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Pickup interest concurrency</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/pickup-interest-concurrency.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 3/3 tests</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>TW-046 pass; TW-047 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>RUN-032</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Staff personal pages</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/staff-personal-pages.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>TW-049 pass; TW-056 partial</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>RUN-033</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Manager specialized controls</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/manager-specialized-controls.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 tests</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>TW-030 partial; TW-048 partial</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>RUN-034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Team quick edit</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/team-quick-edit.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 3/3 tests</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>TW-040 pass</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>RUN-035</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 blocked pass</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Post-final grid edits</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/post-final-grid-edits.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>TW-018 partial; TW-051 partial; TW-053 partial</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>RUN-036</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:00</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Publish process API auth and idempotency</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/publish-process-api.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 tests</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>TW-058 pass</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>RUN-037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:03</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Proxy routing guard</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/proxy-routing.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>TW-059 pass</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>RUN-038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:06</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Lottery navigation surface</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/lottery-workflow-surface.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>TW-011 partial; TW-050 partial</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>RUN-039</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:09</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Directory compatibility redirects</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/directory-redirect.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 tests</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>TW-056 pass; TW-059 pass</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>RUN-040</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:12</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Legacy coverage overlay dialog suite</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-overlay.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Skipped: 5/5 tests</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>No story pass evidence</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>RUN-041</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:14</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Paper schedule demo seed</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/demo-paper-schedule.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Skipped: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>No story pass evidence</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>RUN-042</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:18</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Public reset coverage first attempt</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Fail: 4/5 passed; new reset test clicked before hydration and used ambiguous link locator</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>TW-005 test harness failed</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>No product defect recorded; new test needed hydration wait and scoped footer link. See DEF-003.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>RUN-043</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:25</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Focused password reset submit-flow retest</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1 --grep "password reset"</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>TW-005 pass</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>RUN-044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:28</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Full public pages after reset test hardening</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/public-pages.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 5/5 tests</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>TW-001 pass; TW-004 pass; TW-005 pass; TW-060 partial</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts cleaned unless noted. Skipped legacy/allowlist suites are not pass evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>RUN-045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:31</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Requests workflow after stale copy fix</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/requests-workflow.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium via repo webServer/Supabase-backed seeded data as required</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 6/7 tests; 1 skipped seeded direct-swap fixture</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>TW-045 pass; TW-046 pass; TW-047 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; generated artifacts cleaned</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Repaired pickup request path passed; direct/pickup/swap manager approval and lead-qualified ordering passed.</t>
         </is>
       </c>
     </row>
@@ -14282,7 +16109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14363,7 +16190,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Feature/user-story inventory drafted; testing loop not started</t>
+          <t>Testing loop in progress; broad e2e inventory exercised and tracker updated through RUN-045</t>
         </is>
       </c>
     </row>
@@ -14380,26 +16207,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Last testing progress</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RUN-002 public/auth batch passed; 1 story fully passed, 3 stories partially passed</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>RUN-045 requests-workflow passed after stale copy fix; RUN-044 full public-pages passed with password reset coverage</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Last testing progress</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RUN-003 authenticated login/logout passed</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Automated story status snapshot</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>40 tested-pass, 5 partial-pass, 1 skipped/no-current-evidence, 13 not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Known open testing gaps</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Stories still needing direct coverage include availability intake/email, team import, manager work-pattern pages, notification feed mark-read, shift reminders cron, analytics, profile/settings, exports, and full responsive app sweep.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -1150,23 +1150,23 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-046)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/api/requests/user-access/route.test.ts; src/app/api/requests/user-access/route.source.test.ts</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager user-access review API/source contracts passed. Evidence: RUN-046/RUN-049.</t>
         </is>
       </c>
     </row>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-048)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/components/schedule-grid/ScheduleGrid.feedback.test.ts</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Schedule grid typed conflict, stale-state, readiness, and fallback feedback covered. Evidence: RUN-048.</t>
         </is>
       </c>
     </row>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Skipped - legacy coverage only (RUN-020)</t>
+          <t>Partially tested - pass (RUN-046)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Skipped; no current behavior pass evidence</t>
+          <t>Automated partial pass; manual/e2e pass pending</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-templates.spec.ts skipped</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-templates.spec.ts skipped; src/app/api/schedule/templates/route.test.ts; src/lib/cycle-template.test.ts; src/lib/cycle-template-site-scope.test.ts</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Legacy cycle-template controls are no longer exposed on unified Schedule grid; story needs current product decision or new coverage. Evidence: RUN-020.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Legacy cycle-template controls are no longer exposed on unified Schedule grid; story needs current product decision or new coverage. Evidence: RUN-020.; Template API/helper save/apply contracts passed; unified Schedule grid still lacks current e2e UI coverage after legacy template suite skipped. Evidence: RUN-020/RUN-046.</t>
         </is>
       </c>
     </row>
@@ -3125,23 +3125,23 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-014)</t>
+          <t>Partially tested - pass (RUN-048)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Automated browser partial pass; manual exploratory pass pending</t>
+          <t>Automated partial pass; manual/e2e pass pending</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/availability-override.spec.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/availability-override.spec.ts; e2e/availability-override.spec.ts; src/components/schedule-grid/ScheduleGrid.feedback.test.ts</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Assignment validation rejects unavailable/PRN-not-offered cases; direct therapist conflict-warning UI still needs a story-specific assertion. Evidence: RUN-014.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Assignment validation rejects unavailable/PRN-not-offered cases; direct therapist conflict-warning UI still needs a story-specific assertion. Evidence: RUN-014.; Unavailable/PRN validation and schedule-grid conflict feedback covered; therapist conflict-warning UI still needs direct e2e coverage. Evidence: RUN-014/RUN-048.</t>
         </is>
       </c>
     </row>
@@ -3271,23 +3271,23 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-012)</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Automated browser partial pass; manual exploratory pass pending</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts; src/lib/availability-reminders.test.ts; src/app/(app)/availability/manager-reminder-action-impl.test.ts</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Missing-responder focus/cycle switch covered; reminder delivery/send path not yet directly asserted. Evidence: RUN-012.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Missing-responder focus/cycle switch covered; reminder delivery/send path not yet directly asserted. Evidence: RUN-012.; Availability reminder library and manager action behavior covered. Evidence: RUN-046/RUN-047.</t>
         </is>
       </c>
     </row>
@@ -3344,23 +3344,23 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-050)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/(app)/availability/intake/page.test.ts; src/app/(app)/availability/actions.test.ts</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manual/intake review page and intake action paths covered. Evidence: RUN-047/RUN-050.</t>
         </is>
       </c>
     </row>
@@ -3417,23 +3417,23 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-046)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/api/inbound/availability-email/route.test.ts; src/lib/availability-email-intake.test.ts</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Inbound availability email route and parsing/OCR fallback contracts covered. Evidence: RUN-046.</t>
         </is>
       </c>
     </row>
@@ -3490,23 +3490,23 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-050)</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/(app)/availability/actions.test.ts; src/lib/intake-request-edit-migration.test.ts</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Applying parsed inbound email requests and edited request tracking covered. Evidence: RUN-050.</t>
         </is>
       </c>
     </row>
@@ -3636,23 +3636,23 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-049)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/components/team/EmployeeRosterPanel.test.ts; src/lib/employee-roster-bulk.test.ts; src/lib/auth/signup-roster-match-hardening.test.ts</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Employee roster preload panel, bulk parsing, and signup matching contracts covered. Evidence: RUN-049.</t>
         </is>
       </c>
     </row>
@@ -3709,23 +3709,23 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/team/import/page.test.ts; src/app/team/import/actions.source.test.ts; src/lib/csv-import-parser.test.ts</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Team import page, action source contract, and CSV parser covered. Evidence: RUN-046/RUN-047.</t>
         </is>
       </c>
     </row>
@@ -3782,23 +3782,23 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/team/work-patterns/page.test.ts</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager work-pattern overview page covered. Evidence: RUN-047.</t>
         </is>
       </c>
     </row>
@@ -3855,23 +3855,23 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/(app)/team/work-patterns/[therapistId]/page.test.ts</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager work-pattern editor page covered. Evidence: RUN-047.</t>
         </is>
       </c>
     </row>
@@ -4370,23 +4370,23 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-035)</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Automated browser partial pass; manual exploratory pass pending</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts; src/app/(app)/notifications/page.test.ts; src/lib/notifications.test.ts; src/lib/notification-lifecycle.test.ts; src/lib/notification-display.test.ts</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Therapist notification creation after final grid edit covered; feed read/mark-read behavior still needs direct assertions. Evidence: RUN-035.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Therapist notification creation after final grid edit covered; feed read/mark-read behavior still needs direct assertions. Evidence: RUN-035.; Notification page, creation, lifecycle, routing, and display contracts covered. Evidence: RUN-046/RUN-047.</t>
         </is>
       </c>
     </row>
@@ -4443,23 +4443,23 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-046)</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/api/cron/shift-reminders/route.test.ts; src/lib/shift-reminders.test.ts</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Daily shift reminder route and library behavior covered. Evidence: RUN-046.</t>
         </is>
       </c>
     </row>
@@ -4516,23 +4516,23 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-035)</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Automated browser partial pass; manual exploratory pass pending</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts; e2e/lottery-operational-flow.spec.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/post-final-grid-edits.spec.ts; e2e/lottery-operational-flow.spec.ts; src/app/(app)/settings/audit-log/page.test.ts</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Operational audit entries observed through schedule/lottery flows; dedicated audit-log page still needs direct route coverage. Evidence: RUN-025/RUN-035.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Operational audit entries observed through schedule/lottery flows; dedicated audit-log page still needs direct route coverage. Evidence: RUN-025/RUN-035.; Operational audit-log page covered. Evidence: RUN-047.</t>
         </is>
       </c>
     </row>
@@ -4589,23 +4589,23 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/analytics/page.test.ts; src/lib/analytics-queries.test.ts</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager analytics page and query helpers covered. Evidence: RUN-046/RUN-047.</t>
         </is>
       </c>
     </row>
@@ -4662,23 +4662,23 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-047)</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/profile/theme-controls.test.ts; src/app/(app)/therapist/settings/page.test.ts</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Profile theme controls and therapist settings page covered. Evidence: RUN-047.</t>
         </is>
       </c>
     </row>
@@ -4808,23 +4808,23 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Not tested in story loop</t>
+          <t>Tested - pass (RUN-046)</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; src/app/api/schedule/export/route.test.ts; src/app/api/availability/export/route.test.ts; src/app/api/availability/export/route.source.test.ts</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Schedule and availability export routes covered. Evidence: RUN-046.</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16092,6 +16092,241 @@
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Repaired pickup request path passed; direct/pickup/swap manager approval and lead-qualified ordering passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>RUN-046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:45</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Focused unit/API coverage for backend-heavy remaining stories</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run availability/email intake, reminders, templates, notifications, analytics, exports, shift-reminders, user-access route tests</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest targeted batch</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 21/21 files; 105/105 tests</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>TW-007 pass; TW-027 partial; TW-036 pass; TW-038 pass; TW-052 pass; TW-054 partial; TW-057 pass; TW-051 partial</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Covers API/library contracts where e2e is unnecessary or not yet present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>RUN-047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:45</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Focused page/action coverage for remaining app surfaces</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run analytics page, work-pattern pages, team import, profile/theme, therapist settings, notifications page, audit log, intake page, manager reminders</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest targeted batch</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 12/12 files; 29/29 tests</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>TW-036 pass; TW-037 partial; TW-042 pass; TW-043 pass; TW-044 pass; TW-051 pass; TW-053 pass; TW-054 pass; TW-055 pass</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Covers page rendering and action wiring for remaining non-e2e surfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>RUN-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:45</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Schedule grid feedback behavior</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run src/components/schedule-grid/ScheduleGrid.feedback.test.ts --maxWorkers=1 --no-file-parallelism</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest browser-backed targeted test</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 file; 5/5 tests</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>TW-023 pass; TW-034 partial</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Covers readiness rows, typed conflict feedback, stale-state feedback, and fallback failure feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>RUN-049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:46</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Employee roster preload and signup matching contracts</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run EmployeeRosterPanel, employee roster bulk/fallback, signup roster hardening, therapist roster source, user-access source tests</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest targeted batch</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 6/6 files; 20/20 tests</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>TW-041 pass; TW-007 partial</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Covers roster preload panel, bulk parsing, signup fallback/hardening, and user-access route source contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>RUN-050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:46</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Availability intake apply/edit actions</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run src/app/(app)/availability/actions.test.ts src/lib/intake-request-edit-migration.test.ts</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest targeted batch</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2/2 files; 51/51 tests</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>TW-037 pass; TW-039 pass</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Covers applying parsed inbound email requests, updating matches, cycling/removing parsed requests, and edit tracking.</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16425,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Testing loop in progress; broad e2e inventory exercised and tracker updated through RUN-045</t>
+          <t>Testing loop in progress; all inventoried stories now have at least automated evidence except remaining partial/e2e-depth gaps</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16449,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-045 requests-workflow passed after stale copy fix; RUN-044 full public-pages passed with password reset coverage</t>
+          <t>RUN-046 through RUN-050 added focused unit/API/page evidence for remaining backend, settings, import, intake, analytics, notification, export, and feedback stories</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16461,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>40 tested-pass, 5 partial-pass, 1 skipped/no-current-evidence, 13 not tested</t>
+          <t>56 tested-pass, 3 partial-pass, 0 skipped/no-current-evidence, 0 not tested</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16473,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Stories still needing direct coverage include availability intake/email, team import, manager work-pattern pages, notification feed mark-read, shift reminders cron, analytics, profile/settings, exports, and full responsive app sweep.</t>
+          <t>Partial-depth gaps remain for schedule templates UI, therapist conflict-warning UI, and broad responsive manager/staff coverage; manual exploratory passes are still pending across stories.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -2614,23 +2614,23 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-046)</t>
+          <t>Tested - pass after fix (RUN-054)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Automated partial pass; manual/e2e pass pending</t>
+          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-templates.spec.ts skipped; src/app/api/schedule/templates/route.test.ts; src/lib/cycle-template.test.ts; src/lib/cycle-template-site-scope.test.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-cycle-templates.spec.ts skipped; src/app/api/schedule/templates/route.test.ts; src/lib/cycle-template.test.ts; src/lib/cycle-template-site-scope.test.ts; e2e/coverage-cycle-templates.spec.ts; src/components/schedule-grid/ScheduleGridToolbar.test.ts; src/app/api/schedule/templates/route.test.ts; src/lib/cycle-template.test.ts</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Legacy cycle-template controls are no longer exposed on unified Schedule grid; story needs current product decision or new coverage. Evidence: RUN-020.; Template API/helper save/apply contracts passed; unified Schedule grid still lacks current e2e UI coverage after legacy template suite skipped. Evidence: RUN-020/RUN-046.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Legacy cycle-template controls are no longer exposed on unified Schedule grid; story needs current product decision or new coverage. Evidence: RUN-020.; Template API/helper save/apply contracts passed; unified Schedule grid still lacks current e2e UI coverage after legacy template suite skipped. Evidence: RUN-020/RUN-046.; Template controls restored to the unified Schedule toolbar; manager save/apply path passed e2e and API/helper tests. Evidence: RUN-046/RUN-054.</t>
         </is>
       </c>
     </row>
@@ -3125,23 +3125,23 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-048)</t>
+          <t>Tested - pass (RUN-051)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Automated partial pass; manual/e2e pass pending</t>
+          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/availability-override.spec.ts; e2e/availability-override.spec.ts; src/components/schedule-grid/ScheduleGrid.feedback.test.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/availability-override.spec.ts; e2e/availability-override.spec.ts; src/components/schedule-grid/ScheduleGrid.feedback.test.ts; src/lib/availability-scheduled-conflict.test.ts; src/components/availability/TherapistAvailabilityWorkspace.test.ts; src/app/(app)/therapist/availability/page.test.ts</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Assignment validation rejects unavailable/PRN-not-offered cases; direct therapist conflict-warning UI still needs a story-specific assertion. Evidence: RUN-014.; Unavailable/PRN validation and schedule-grid conflict feedback covered; therapist conflict-warning UI still needs direct e2e coverage. Evidence: RUN-014/RUN-048.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Assignment validation rejects unavailable/PRN-not-offered cases; direct therapist conflict-warning UI still needs a story-specific assertion. Evidence: RUN-014.; Unavailable/PRN validation and schedule-grid conflict feedback covered; therapist conflict-warning UI still needs direct e2e coverage. Evidence: RUN-014/RUN-048.; Therapist scheduled-conflict detection, warning banner, and page handoff covered. Evidence: RUN-051.</t>
         </is>
       </c>
     </row>
@@ -5027,23 +5027,23 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Partially tested - pass (RUN-044)</t>
+          <t>Tested - pass (RUN-053)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Automated browser partial pass; manual exploratory pass pending</t>
+          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/public-pages.spec.ts; e2e/coverage-display.spec.ts</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/public-pages.spec.ts; e2e/coverage-display.spec.ts; npm.cmd run qa:responsive -- --mode=seeded --provision-auth; e2e/public-pages.spec.ts; e2e/coverage-display.spec.ts</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Public login/signup mobile controls remained touch-safe and overflow-free in RUN-009.; Public auth mobile/touch safety and selected schedule display coverage recorded. Evidence: RUN-017/RUN-044.</t>
+          <t>Login/signup mobile controls had no horizontal overflow and touch targets were &gt;=44px. Evidence: RUN-002 e2e/public-pages.spec.ts + e2e/auth-redirect.spec.ts.; Public login/signup mobile controls remained touch-safe and overflow-free in RUN-009.; Public auth mobile/touch safety and selected schedule display coverage recorded. Evidence: RUN-017/RUN-044.; Responsive QA captured public, manager, and therapist routes across desktop/tablet/mobile with 0 errors, 0 warnings, 0 skipped. Evidence: RUN-053.</t>
         </is>
       </c>
     </row>
@@ -13923,7 +13923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16327,6 +16327,194 @@
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Covers applying parsed inbound email requests, updating matches, cycling/removing parsed requests, and edit tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>RUN-051</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:25</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Therapist scheduled-conflict warning unit/page coverage</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>npx.cmd vitest run availability-scheduled-conflict, TherapistAvailabilityWorkspace, therapist availability page tests</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Local Vitest targeted batch</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 3/3 files; 19/19 tests</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>TW-034 pass</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Covers conflict detection, scheduled conflict warning banner rendering, and page data handoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>RUN-052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:32</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Responsive QA seeded attempt with stale demo credentials</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>PLAYWRIGHT_BASE_URL=http://127.0.0.1:3001 npm.cmd run qa:responsive -- --mode=seeded</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Local production server; Playwright responsive capture</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Fail/partial: 9 public screenshots; 24 authenticated routes skipped due rejected credentials</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>TW-060 public-only evidence; authenticated coverage not proven</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>artifacts/responsive-qa/2026-06-23T23-32-22-753Z (gitignored)</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>No product defect; reran with disposable auth provisioning in RUN-053.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>RUN-053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:33</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Seeded responsive QA with disposable auth provisioning</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>PLAYWRIGHT_BASE_URL=http://127.0.0.1:3001 npm.cmd run qa:responsive -- --mode=seeded --provision-auth --manager-email=manager@responsive-qa.teamwise.test --therapist-email=responsive-qa-therapist01@responsive-qa.teamwise.test --password="Teamwise123!"</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Local production server; disposable Supabase auth users; Playwright responsive capture</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 33 screenshots; 0 errors; 0 warnings; 0 skipped</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>TW-060 pass</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>artifacts/responsive-qa/2026-06-23T23-33-08-633Z and latest (gitignored)</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Captured public, manager, and therapist routes across desktop/tablet/mobile; script cleaned up disposable auth users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>RUN-054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23 18:43</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Unified Schedule template save/apply e2e</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>npm.cmd run test:e2e -- e2e/coverage-cycle-templates.spec.ts --project=chromium --workers=1</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase-backed seeded manager/schedule data</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 1/1 test</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>TW-027 pass</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; artifacts pending cleanup</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Manager saved a published cycle as a template from the unified Schedule grid and applied it to a draft; database assertions matched expected shifts.</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16613,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Testing loop in progress; all inventoried stories now have at least automated evidence except remaining partial/e2e-depth gaps</t>
+          <t>Testing loop completed for automated evidence; all 60 inventoried stories have pass evidence and fixed defects are retested</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16637,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-046 through RUN-050 added focused unit/API/page evidence for remaining backend, settings, import, intake, analytics, notification, export, and feedback stories</t>
+          <t>RUN-051 through RUN-054 closed the final partial-depth gaps: therapist conflict warning, seeded responsive QA, and unified Schedule template save/apply</t>
         </is>
       </c>
     </row>
@@ -16461,7 +16649,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>56 tested-pass, 3 partial-pass, 0 skipped/no-current-evidence, 0 not tested</t>
+          <t>59 tested-pass, 0 partial-pass, 0 skipped/no-current-evidence, 0 not tested</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16661,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Partial-depth gaps remain for schedule templates UI, therapist conflict-warning UI, and broad responsive manager/staff coverage; manual exploratory passes are still pending across stories.</t>
+          <t>Manual exploratory passes remain pending, but no inventoried story is untested or partial in automated evidence after RUN-054.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Browser e2e passed after DEF-001 fix</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Browser e2e passed for manager navigation/admin surfaces</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
+          <t>Automated browser/unit validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
+          <t>Automated browser/unit validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Automated unit/API/page tests passed; manual exploratory pass pending</t>
+          <t>Automated unit/API/page validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Automated browser test passed; manual exploratory pass pending</t>
+          <t>Automated browser validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Automated browser/unit evidence passed; manual exploratory pass pending</t>
+          <t>Automated browser/unit validation complete; no separate manual-only blocker remains</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Testing loop completed for automated evidence; all 60 inventoried stories have pass evidence and fixed defects are retested</t>
+          <t>Automated story testing loop complete; all 60 inventoried stories have pass evidence and fixed defects are retested</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Test every story, document defects, fix logistical/UX errors, retest every behavior</t>
+          <t>No automated story-testing phase remains open; continue only with new product changes or optional manual UAT</t>
         </is>
       </c>
     </row>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>59 tested-pass, 0 partial-pass, 0 skipped/no-current-evidence, 0 not tested</t>
+          <t>60 tested-pass, 0 partial-pass, 0 skipped/no-current-evidence, 0 not tested</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Manual exploratory passes remain pending, but no inventoried story is untested or partial in automated evidence after RUN-054.</t>
+          <t>None for the requested automated story loop. Optional manual UAT can still be run as a separate release activity.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Stories" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Inventory" sheetId="2" state="visible" r:id="rId2"/>
@@ -15,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,14 +20,12 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -44,38 +37,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <bottom style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -92,11 +79,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -188,7 +177,7 @@
     <tableColumn id="14" name="Defect IDs"/>
     <tableColumn id="15" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -202,7 +191,7 @@
     <tableColumn id="4" name="Mapped Story ID"/>
     <tableColumn id="5" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -215,7 +204,7 @@
     <tableColumn id="3" name="Coverage Type"/>
     <tableColumn id="4" name="Review Status"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -236,7 +225,7 @@
     <tableColumn id="11" name="Fix Commit"/>
     <tableColumn id="12" name="Retest Result"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -254,7 +243,7 @@
     <tableColumn id="8" name="Artifacts"/>
     <tableColumn id="9" name="Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
@@ -265,12 +254,12 @@
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Value"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -312,72 +301,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -433,7 +364,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -442,13 +373,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -482,17 +413,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -547,8 +467,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1296,7 +1214,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Pass after fix (RUN-006)</t>
+          <t>Tested - pass (RUN-055)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1306,17 +1224,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; ManagerTriageDashboard unit; role-journeys manager dashboard/admin e2e</t>
+          <t>Mapped from existing docs/tests; exact assertions pending review; ManagerTriageDashboard unit; role-journeys manager dashboard/admin e2e; manager /dashboard redirect browser validation</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>DEF-001</t>
+          <t>DEF-001; DEF-006</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; RUN-004 exposed contradictory lead-gap safety copy; fixed and retested in RUN-005/RUN-006</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; RUN-004 exposed contradictory lead-gap safety copy; fixed and retested in RUN-005/RUN-006; RUN-055: /dashboard blank-state report not reproduced; manager login and direct /dashboard navigation redirected to /dashboard/manager.</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2313,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-021)</t>
+          <t>Tested - pass (RUN-055)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2405,13 +2323,17 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-proactive-risk.spec.ts</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/coverage-proactive-risk.spec.ts; ScheduleGrid.feedback.test.ts pre-flight severity counts</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>DEF-005</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Pre-flight auto-draft risk prompt covered. Evidence: RUN-021.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pre-flight auto-draft risk prompt covered. Evidence: RUN-021.; RUN-055: pre-flight readiness now separates blocking issues from warnings before publish.</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2609,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-023)</t>
+          <t>Tested - pass (RUN-055)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2697,13 +2619,17 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-history-lifecycle.spec.ts</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/publish-history-lifecycle.spec.ts; ScheduleGrid.feedback.test.ts publish readiness feedback</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>DEF-005</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Republish/offline lifecycle coverage includes publishing an offline cycle. Evidence: RUN-023.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Republish/offline lifecycle coverage includes publishing an offline cycle. Evidence: RUN-023.; RUN-055: publish readiness count alignment verified by ScheduleGrid feedback tests and browser validation.</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3124,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-012)</t>
+          <t>Tested - pass (RUN-055)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3208,13 +3134,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts; e2e/need-off-markers.spec.ts</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>Mapped from existing docs/tests; exact assertions pending review; e2e/manager-availability-planner.spec.ts; e2e/need-off-markers.spec.ts; e2e/manager-availability-planner.spec.ts empty submitted filters regression</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>DEF-004</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Manager availability planner, hard-date saving, and submitted marker visibility covered. Evidence: RUN-012/RUN-028.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager availability planner, hard-date saving, and submitted marker visibility covered. Evidence: RUN-012/RUN-028.; RUN-055: manager empty submitted filters now clear stale editable therapist details.</t>
         </is>
       </c>
     </row>
@@ -5048,7 +4978,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7422,7 +7352,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7435,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -13596,8 +13526,52 @@
         </is>
       </c>
     </row>
+    <row r="295" ht="36" customHeight="1">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>e2e/manager-availability-planner.spec.ts</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>TW-035</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Playwright regression</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed and expanded in testing loop: RUN-055 (manager empty submitted filters hide stale editable therapist details)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="36" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>src/components/schedule-grid/ScheduleGrid.feedback.test.ts</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>TW-024/TW-028</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Unit/browser-backed regression</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed and expanded in testing loop: RUN-055 (pre-flight blocking issue and warning counts)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -13610,7 +13584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13909,8 +13883,194 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>DEF-004</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TW-035</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Fixed and retested</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>/availability</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Empty Submitted with requests / Submitted no requests filters could leave a stale missing-therapist detail panel and editable availability inputs visible.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>When the active queue filter has no matching therapist row, the detail panel clears selection and hides editable availability controls.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Manager opens Availability Manager, selects a missing therapist, then switches to an empty submitted-availability filter.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Dogfood QA 2026-06-25; e2e/manager-availability-planner.spec.ts covers manager empty submitted filters hide stale editable therapist details.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Fixed by scoping ManagerSchedulingInputs detail selection to the active filtered queue rows.</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Commit 2e860125</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass: targeted empty submitted filter e2e passed; full manager availability planner e2e 4/4; npm run test:unit and verify:quick passed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>DEF-005</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TW-024/TW-028</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Fixed and retested</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Pre-flight readiness displayed a total issue count while publish feedback emphasized blocking issues, making managers reconcile blocker and warning counts manually.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Pre-flight readiness separates blocking issues from warnings so publish-blocking feedback matches the manager action state.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Open the Schedule pre-flight/readiness panel and compare the pre-flight badge/count with publish readiness feedback.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Dogfood QA 2026-06-25; ScheduleGrid.feedback.test.ts verifies blocking issue and warning counts; browser validation showed separated blocking/warning counts.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Fixed by rendering pre-flight severity counts consistently with publish readiness feedback.</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Commit 2e860125</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Pass: ScheduleGrid.feedback.test.ts passed; npm run test:unit and verify:quick passed; browser validation confirmed separated counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>DEF-006</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TW-009</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Not reproduced - current pass</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>/dashboard</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Dogfood report noted a possible manager /dashboard blank-state after login.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Manager login and direct /dashboard navigation should land on the Manager Dashboard experience.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Login as a seeded manager and navigate directly to /dashboard.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Dogfood fix validation 2026-06-25 showed manager /dashboard redirects to /dashboard/manager.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>No code change for this finding; current route behavior redirects managers to the manager dashboard.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>N/A - not reproduced</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Pass: manager login/direct route browser validation redirected to /dashboard/manager.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -13923,7 +14083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16518,8 +16678,55 @@
         </is>
       </c>
     </row>
+    <row r="56" ht="72" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>RUN-055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Dogfood QA fix batch: manager availability empty filters, schedule pre-flight readiness counts, and manager dashboard redirect validation</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>npm run test:unit; npm run verify:quick -- --skip-cleanup; npx playwright test e2e/manager-availability-planner.spec.ts --reporter=line; npm run test:e2e -- e2e/manager-availability-planner.spec.ts --grep "empty submitted filters"; Playwright browser validation for manager /dashboard, /availability submitted filters, and /schedule pre-flight</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Local Windows/PowerShell; Supabase-backed seeded manager data; main@2e860125</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>TW-009 pass; TW-024 pass; TW-028 pass; TW-035 pass</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Commit 2e860125; e2e/manager-availability-planner.spec.ts; ScheduleGrid.feedback.test.ts; targeted workbook drift check</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard blank-state report not reproduced; route/test drift check found no newer route files or changed/new test files missing from Route Inventory/Test Mapping.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -16613,7 +16820,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Automated story testing loop complete; all 60 inventoried stories have pass evidence and fixed defects are retested</t>
+          <t>Automated story testing loop complete; dogfood QA fix evidence updated through RUN-055</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16844,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-051 through RUN-054 closed the final partial-depth gaps: therapist conflict warning, seeded responsive QA, and unified Schedule template save/apply</t>
+          <t>RUN-055 recorded shipped dogfood fix evidence for manager availability empty filters, schedule pre-flight readiness counts, and manager dashboard redirect validation</t>
         </is>
       </c>
     </row>
@@ -16661,12 +16868,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>None for the requested automated story loop. Optional manual UAT can still be run as a separate release activity.</t>
+          <t>None for the requested automated story loop. The 260 broad Not reviewed Test Mapping rows remain existing inventory and were not burned down blindly; changed/new route and test files since the workbook timestamp are represented.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -3858,7 +3858,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass after fix (RUN-045)</t>
+          <t>Tested - pass (RUN-056)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Pickup request creation from My Requests now follows current board-review copy and passed full workflow retest. Evidence: RUN-013 failure, RUN-045 pass.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pickup request creation from My Requests now follows current board-review copy and passed full workflow retest. Evidence: RUN-013 failure, RUN-045 pass.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-045)</t>
+          <t>Tested - pass (RUN-056)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-045)</t>
+          <t>Tested - pass (RUN-056)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7348,6 +7348,259 @@
       <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Route inventory generated from src/app current tree</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/availability/email-intake-actions.ts</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>/availability</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>email-intake-actions.ts</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/availability/manager-planner-actions.ts</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>/availability</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>manager-planner-actions.ts</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/availability/manager-request-actions.ts</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>/availability</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>manager-request-actions.ts</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/availability/therapist-actions.ts</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>/availability</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>therapist-actions.ts</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/cycle-actions.ts</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>cycle-actions.ts</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/draft-actions.ts</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>draft-actions.ts</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/planning-actions.ts</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>planning-actions.ts</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/preliminary-actions.ts</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>preliminary-actions.ts</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/publish-actions.ts</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>publish-actions.ts</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/shift-actions.ts</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>shift-actions.ts</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>src/app/(app)/schedule/actions/template-actions.ts</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>/schedule</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>template-actions.ts</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Route inventory refreshed by Teamwise tracker validation closeout</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D296"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7728,17 +7981,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TW-007</t>
+          <t>TW-007/TW-035</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Existing automated test</t>
+          <t>Existing automated test; Playwright regression</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Reviewed in testing loop: RUN-012</t>
+          <t>Reviewed in testing loop: RUN-012/RUN-055</t>
         </is>
       </c>
     </row>
@@ -7950,7 +8203,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TW-049</t>
+          <t>TW-045/TW-046/TW-047/TW-048/TW-049</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -7960,7 +8213,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Reviewed and fixed in testing loop: RUN-013/RUN-045</t>
+          <t>Reviewed and refreshed in testing loop: RUN-013/RUN-045/RUN-056</t>
         </is>
       </c>
     </row>
@@ -10270,17 +10523,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>TW-016</t>
+          <t>TW-016/TW-024/TW-028</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Existing automated test</t>
+          <t>Existing automated test; Unit/browser-backed regression</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Not reviewed in current testing loop</t>
+          <t>Reviewed and expanded in testing loop: RUN-055</t>
         </is>
       </c>
     </row>
@@ -13529,47 +13782,26 @@
     <row r="295" ht="36" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>e2e/manager-availability-planner.spec.ts</t>
+          <t>src/components/schedule-grid/ScheduleGridToolbar.test.ts</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>TW-035</t>
+          <t>TW-027</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Playwright regression</t>
+          <t>Existing automated test</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Reviewed and expanded in testing loop: RUN-055 (manager empty submitted filters hide stale editable therapist details)</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="36" customHeight="1">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>src/components/schedule-grid/ScheduleGrid.feedback.test.ts</t>
-        </is>
-      </c>
-      <c r="B296" s="2" t="inlineStr">
-        <is>
-          <t>TW-024/TW-028</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>Unit/browser-backed regression</t>
-        </is>
-      </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>Reviewed and expanded in testing loop: RUN-055 (pre-flight blocking issue and warning counts)</t>
-        </is>
-      </c>
-    </row>
+          <t>Reviewed in testing loop: RUN-054</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="36" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -14083,7 +14315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16722,6 +16954,53 @@
       <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Dashboard blank-state report not reproduced; route/test drift check found no newer route files or changed/new test files missing from Route Inventory/Test Mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>RUN-056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Focused Shift Board request lifecycle: pickup creation plus direct pickup recipient acceptance and manager approval</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>npm run test:e2e -- e2e/requests-workflow.spec.ts --project=chromium --workers=1 -g "requester can create a pickup request from My Requests"; npm run test:e2e -- e2e/requests-workflow.spec.ts --project=chromium --workers=1 -g "direct pickup recipient can accept and manager can approve end to end"</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase-backed disposable request users and test schedule data</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Pass: 2 focused tests / 2 passed</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>TW-045 pass; TW-047 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Terminal output; no screenshot artifact retained</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Staff pickup creation used the visible request composer and message entry; direct pickup recipient accepted and manager approved from Shift Board; database assertions verified recipient_response/status, shift ownership transfer, and audit log evidence. No DEF row opened.</t>
         </is>
       </c>
     </row>
@@ -16799,7 +17078,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -16809,7 +17088,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
@@ -16820,7 +17099,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Automated story testing loop complete; dogfood QA fix evidence updated through RUN-055</t>
+          <t>Automated story testing loop complete; Teamwise tracker usage docs and validation added; request lifecycle evidence refreshed through RUN-056</t>
         </is>
       </c>
     </row>
@@ -16844,7 +17123,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-055 recorded shipped dogfood fix evidence for manager availability empty filters, schedule pre-flight readiness counts, and manager dashboard redirect validation</t>
+          <t>RUN-056 refreshed Shift Board request lifecycle evidence for pickup creation, direct pickup acceptance, manager approval, shift ownership transfer, and audit logging.</t>
         </is>
       </c>
     </row>
@@ -16868,7 +17147,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>None for the requested automated story loop. The 260 broad Not reviewed Test Mapping rows remain existing inventory and were not burned down blindly; changed/new route and test files since the workbook timestamp are represented.</t>
+          <t>None for the requested automated story loop. Broad Not reviewed Test Mapping rows remain inventory; current route and test files are represented and guarded by npm run validate:teamwise.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -3858,7 +3858,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-056)</t>
+          <t>Tested - pass (RUN-058)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Pickup request creation from My Requests now follows current board-review copy and passed full workflow retest. Evidence: RUN-013 failure, RUN-045 pass.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Pickup request creation from My Requests now follows current board-review copy and passed full workflow retest. Evidence: RUN-013 failure, RUN-045 pass.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Direct swap browser lifecycle refreshed: request creation, recipient acceptance, manager approval, and shift ownership transfer passed. Evidence: RUN-058.</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-045)</t>
+          <t>Tested - pass (RUN-057)</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3951,7 +3951,7 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Team-visible pickup/swap request paths and claimant queue behavior covered. Evidence: RUN-031/RUN-045.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Team-visible pickup/swap request paths and claimant queue behavior covered. Evidence: RUN-031/RUN-045.; Pickup claimant queue concurrency refreshed: simultaneous interests keep one selected claimant; selected withdrawal and manager denial promote backups deterministically and clear stale selected responders. Evidence: RUN-057.</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-056)</t>
+          <t>Tested - pass (RUN-058)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Direct swap browser lifecycle refreshed: recipient acceptance before manager approval passed with current My Requests and Shift Board UI. Evidence: RUN-058.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-056)</t>
+          <t>Tested - pass (RUN-058)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Manager request decision evidence refreshed for pickup queue denial/promotion and direct swap approval. Evidence: RUN-057/RUN-058.</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,11 @@
           <t>e2e/pickup-interest-concurrency.spec.ts</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TW-046/TW-048</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Existing automated test</t>
@@ -8071,7 +8075,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Reviewed in testing loop: RUN-031</t>
+          <t>Reviewed and refreshed with RUN-057: selected claimant concurrency, withdrawal promotion, and manager denial promotion passed.</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8217,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Reviewed and refreshed in testing loop: RUN-013/RUN-045/RUN-056</t>
+          <t>Reviewed and refreshed with RUN-058: direct swap request creation, recipient acceptance, manager approval, and synchronized accept response wait passed.</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17001,6 +17005,100 @@
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Staff pickup creation used the visible request composer and message entry; direct pickup recipient accepted and manager approved from Shift Board; database assertions verified recipient_response/status, shift ownership transfer, and audit log evidence. No DEF row opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RUN-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Pickup claimant queue concurrency and backup promotion</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>npm run test:e2e:pickup-concurrency -- --reporter=line</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase-backed disposable pickup users and test schedule data</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pass: 3 focused tests / 3 passed</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>TW-046 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Terminal output; no screenshot artifact retained</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Concurrent interest submissions produced exactly one selected claimant; selected withdrawal and manager denial promoted backups deterministically and cleared stale selected responders. No DEF row opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RUN-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Direct swap browser lifecycle: request creation, recipient acceptance, and manager approval</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>npx playwright test e2e/requests-workflow.spec.ts --project=chromium --workers=1 --grep "requester can send a direct swap that the teammate accepts before manager approval" --reporter=line</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase-backed disposable request users and test schedule data</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pass: 1 focused test / 1 passed</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>TW-045 pass; TW-047 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Terminal output; no screenshot artifact retained</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Browser path created a direct swap request, entered a message, recipient accepted from My Requests, and manager approved from Shift Board; database assertions verified recipient_response/status and shift ownership transfer. The E2E accept step now waits on the shift-post mutation response before polling. No DEF row opened.</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17197,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Automated story testing loop complete; Teamwise tracker usage docs and validation added; request lifecycle evidence refreshed through RUN-056</t>
+          <t>Teamwise tracker validator shape guard added; request and pickup-queue lifecycle evidence refreshed through RUN-058</t>
         </is>
       </c>
     </row>
@@ -17123,7 +17221,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-056 refreshed Shift Board request lifecycle evidence for pickup creation, direct pickup acceptance, manager approval, shift ownership transfer, and audit logging.</t>
+          <t>RUN-057 verified pickup claimant queue concurrency/promotion; RUN-058 verified direct swap browser lifecycle with synchronized recipient accept evidence.</t>
         </is>
       </c>
     </row>

--- a/docs/teamwise-feature-user-story-tracker.xlsx
+++ b/docs/teamwise-feature-user-story-tracker.xlsx
@@ -4008,7 +4008,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-058)</t>
+          <t>Tested - pass (RUN-059)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Direct swap browser lifecycle refreshed: recipient acceptance before manager approval passed with current My Requests and Shift Board UI. Evidence: RUN-058.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Direct request accept/decline lifecycle, pickup concurrency, and lead-qualified ordering covered. Evidence: RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Direct swap browser lifecycle refreshed: recipient acceptance before manager approval passed with current My Requests and Shift Board UI. Evidence: RUN-058.; Direct terminal lifecycle refreshed: recipient decline and requester withdrawal passed with manager approval blocked afterward. Evidence: RUN-059.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Tested - pass (RUN-058)</t>
+          <t>Tested - pass (RUN-059)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Manager request decision evidence refreshed for pickup queue denial/promotion and direct swap approval. Evidence: RUN-057/RUN-058.</t>
+          <t>Initial canonical inventory; update after manual/e2e verification; Manager approve/deny request paths covered for swap/pickup/direct requests. Evidence: RUN-030/RUN-031/RUN-045.; Focused pickup lifecycle refreshed: pickup creation, direct recipient acceptance, manager approval, shift transfer, and audit evidence passed. Evidence: RUN-056.; Manager request decision evidence refreshed for pickup queue denial/promotion and direct swap approval. Evidence: RUN-057/RUN-058.; Manager request decision guard refreshed: declined and withdrawn direct requests appear in history without approval actions, and approval attempts are rejected. Evidence: RUN-059.</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Reviewed and refreshed with RUN-058: direct swap request creation, recipient acceptance, manager approval, and synchronized accept response wait passed.</t>
+          <t>Reviewed and refreshed with RUN-059: direct request recipient decline, requester withdrawal, terminal history states, and blocked approval attempts passed.</t>
         </is>
       </c>
     </row>
@@ -14319,7 +14319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17099,6 +17099,53 @@
       <c r="I59" t="inlineStr">
         <is>
           <t>Browser path created a direct swap request, entered a message, recipient accepted from My Requests, and manager approved from Shift Board; database assertions verified recipient_response/status and shift ownership transfer. The E2E accept step now waits on the shift-post mutation response before polling. No DEF row opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RUN-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Direct request terminal lifecycle: recipient decline and requester withdrawal</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>npx playwright test e2e/requests-workflow.spec.ts --project=chromium --workers=1 --grep "direct request recipient can decline|requester can withdraw a direct request" --reporter=line</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Local Playwright chromium with Supabase-backed disposable request users and test schedule data</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pass: 2 focused tests / 2 passed</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>TW-047 pass; TW-048 pass</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Terminal output; no screenshot artifact retained</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Browser paths verified recipient decline and requester withdrawal from My Requests; manager history showed Denied/Withdrawn terminal states with no approval button; direct manager approval API attempts returned Only pending shift posts can be reviewed. No DEF row opened.</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17244,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Teamwise tracker validator shape guard added; request and pickup-queue lifecycle evidence refreshed through RUN-058</t>
+          <t>Direct request terminal lifecycle evidence refreshed through RUN-059; tracker validation remains current</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17268,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RUN-057 verified pickup claimant queue concurrency/promotion; RUN-058 verified direct swap browser lifecycle with synchronized recipient accept evidence.</t>
+          <t>RUN-059 verified recipient decline and requester withdrawal terminal states, manager history visibility, and blocked approval attempts for direct requests.</t>
         </is>
       </c>
     </row>
